--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week04/titles.xlsx
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ששון שאולוב - מלי מלי</v>
+        <v>קרן קריספיל - עד שמצאתי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409712&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409722&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ששון שאולוב - מלי מלי</v>
+        <v>קרן קריספיל - עד שמצאתי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שי וינר - תן לי</v>
+        <v>סער הדר - טוב לך איתו</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409711&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409721&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שי וינר - תן לי</v>
+        <v>סער הדר - טוב לך איתו</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עדן גולן - מספיק ממך</v>
+        <v>ים רפאלי - ערפדים</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409710&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409720&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>עדן גולן - מספיק ממך</v>
+        <v>ים רפאלי - ערפדים</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>סטטיק - מנדם</v>
+        <v>טל קייסי - בלב הסערה</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409709&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409719&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>סטטיק - מנדם</v>
+        <v>טל קייסי - בלב הסערה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>נעומי טוב אלמליח - מעבר לדמיון</v>
+        <v>אלי בי - רק תני לי סימן</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409708&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409718&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>נעומי טוב אלמליח - מעבר לדמיון</v>
+        <v>אלי בי - רק תני לי סימן</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>יגל יובל שרעבי - מחושך לאור</v>
+        <v>איתי אהרון - אהבה כאב וטעויות</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409707&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409717&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>יגל יובל שרעבי - מחושך לאור</v>
+        <v>איתי אהרון - אהבה כאב וטעויות</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ויולט - לנוע</v>
+        <v>אייל לוי - מדויק</v>
       </c>
       <c r="B8" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409706&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409716&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>ויולט - לנוע</v>
+        <v>אייל לוי - מדויק</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>דניאלה גלבוע - איפה שהכל נגמר</v>
+        <v>אחי נתן - לא בחור דתי</v>
       </c>
       <c r="B9" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409705&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409715&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>דניאלה גלבוע - איפה שהכל נגמר</v>
+        <v>אחי נתן - לא בחור דתי</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אלמוג זגרון - ג׳ורדן</v>
+        <v>אורן כדורי - למה ככה</v>
       </c>
       <c r="B10" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409704&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409714&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אלמוג זגרון - ג׳ורדן</v>
+        <v>אורן כדורי - למה ככה</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אדיר בובליל - בא לי שוב</v>
+        <v>אייל שלום - אתה חי</v>
       </c>
       <c r="B11" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409703&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409713&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,7 +811,7 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אדיר בובליל - בא לי שוב</v>
+        <v>אייל שלום - אתה חי</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קרן קריספיל - עד שמצאתי</v>
+        <v>חיים איפרגן - אשרף טק</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409722&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409731&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-23</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קרן קריספיל - עד שמצאתי</v>
+        <v>חיים איפרגן - אשרף טק</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>סער הדר - טוב לך איתו</v>
+        <v>דוריה חממי - טעויות מהעבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409721&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409730&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-23</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>סער הדר - טוב לך איתו</v>
+        <v>דוריה חממי - טעויות מהעבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ים רפאלי - ערפדים</v>
+        <v>בר צברי - ראש לאריות</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409720&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409729&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-23</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ים רפאלי - ערפדים</v>
+        <v>בר צברי - ראש לאריות</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>טל קייסי - בלב הסערה</v>
+        <v>בן אל תבורי &amp; דנה אינטרנשיונל &amp; אמיר שורוש - מה עושים בלילות</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409719&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409728&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-23</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>טל קייסי - בלב הסערה</v>
+        <v>בן אל תבורי &amp; דנה אינטרנשיונל &amp; אמיר שורוש - מה עושים בלילות</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אלי בי - רק תני לי סימן</v>
+        <v>אמיר ישראל - מי עושה קפה</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409718&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409727&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-23</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אלי בי - רק תני לי סימן</v>
+        <v>אמיר ישראל - מי עושה קפה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>איתי אהרון - אהבה כאב וטעויות</v>
+        <v>אייל ישי - לא דיברנו שנינו</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409717&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409726&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-23</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>איתי אהרון - אהבה כאב וטעויות</v>
+        <v>אייל ישי - לא דיברנו שנינו</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אייל לוי - מדויק</v>
+        <v>אוראל מנצור - מחרוזת נועצת מבט 2026</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409716&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409725&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-23</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אייל לוי - מדויק</v>
+        <v>אוראל מנצור - מחרוזת נועצת מבט 2026</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אחי נתן - לא בחור דתי</v>
+        <v>אבי ביטר - מחרוזת לב פצוע 2026</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409715&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409724&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-23</v>
@@ -735,88 +735,12 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אחי נתן - לא בחור דתי</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אורן כדורי - למה ככה</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-02-22</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409714&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אורן כדורי - למה ככה</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אייל שלום - אתה חי</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-02-22</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409713&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אייל שלום - אתה חי</v>
+        <v>אבי ביטר - מחרוזת לב פצוע 2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week04/titles.xlsx
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>חיים איפרגן - אשרף טק</v>
+        <v>תאיר מרציאנו - מחרוזת שקטים 2026</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409731&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409739&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>חיים איפרגן - אשרף טק</v>
+        <v>תאיר מרציאנו - מחרוזת שקטים 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>דוריה חממי - טעויות מהעבר</v>
+        <v>מרדכי רוט - שורף ובועט</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409730&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409738&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>דוריה חממי - טעויות מהעבר</v>
+        <v>מרדכי רוט - שורף ובועט</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>בר צברי - ראש לאריות</v>
+        <v>מירי מסיקה - גידי</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409729&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409737&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>בר צברי - ראש לאריות</v>
+        <v>מירי מסיקה - גידי</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>בן אל תבורי &amp; דנה אינטרנשיונל &amp; אמיר שורוש - מה עושים בלילות</v>
+        <v>מור מזרחי - מחרוזת דוקטור תציל אותי 2026</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409728&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409736&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>בן אל תבורי &amp; דנה אינטרנשיונל &amp; אמיר שורוש - מה עושים בלילות</v>
+        <v>מור מזרחי - מחרוזת דוקטור תציל אותי 2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אמיר ישראל - מי עושה קפה</v>
+        <v>יניב נסימי - מחרוזת חוזר אל הלב 2026</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409727&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409735&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אמיר ישראל - מי עושה קפה</v>
+        <v>יניב נסימי - מחרוזת חוזר אל הלב 2026</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אייל ישי - לא דיברנו שנינו</v>
+        <v>יותם ששוני - ירח בחלון</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409726&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409734&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אייל ישי - לא דיברנו שנינו</v>
+        <v>יותם ששוני - ירח בחלון</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אוראל מנצור - מחרוזת נועצת מבט 2026</v>
+        <v>יוסף שושן - בוחרת בעצמי</v>
       </c>
       <c r="B8" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409725&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409733&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אוראל מנצור - מחרוזת נועצת מבט 2026</v>
+        <v>יוסף שושן - בוחרת בעצמי</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אבי ביטר - מחרוזת לב פצוע 2026</v>
+        <v>חן ביטון - רבי נחמן אמר</v>
       </c>
       <c r="B9" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409724&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409732&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,7 +735,7 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אבי ביטר - מחרוזת לב פצוע 2026</v>
+        <v>חן ביטון - רבי נחמן אמר</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week04/titles.xlsx
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תאיר מרציאנו - מחרוזת שקטים 2026</v>
+        <v>יאיר שלום - מחרוזת מורל 2026</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-25</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409739&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409747&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תאיר מרציאנו - מחרוזת שקטים 2026</v>
+        <v>יאיר שלום - מחרוזת מורל 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מרדכי רוט - שורף ובועט</v>
+        <v>זיו אלקיים - לא הכרתי את עצמי</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-25</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409738&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409746&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>מרדכי רוט - שורף ובועט</v>
+        <v>זיו אלקיים - לא הכרתי את עצמי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מירי מסיקה - גידי</v>
+        <v>הראל סבג - ענן של רגשות</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-25</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409737&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409745&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>מירי מסיקה - גידי</v>
+        <v>הראל סבג - ענן של רגשות</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מור מזרחי - מחרוזת דוקטור תציל אותי 2026</v>
+        <v>אריאל אזולאי - מראה שעל הקיר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-25</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409736&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409744&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מור מזרחי - מחרוזת דוקטור תציל אותי 2026</v>
+        <v>אריאל אזולאי - מראה שעל הקיר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יניב נסימי - מחרוזת חוזר אל הלב 2026</v>
+        <v>אבירם שוקרון - מיליון דרכים</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-25</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409735&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409743&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יניב נסימי - מחרוזת חוזר אל הלב 2026</v>
+        <v>אבירם שוקרון - מיליון דרכים</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>יותם ששוני - ירח בחלון</v>
+        <v>אליסף עמר - יאללה</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-25</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409734&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409742&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>יותם ששוני - ירח בחלון</v>
+        <v>אליסף עמר - יאללה</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>יוסף שושן - בוחרת בעצמי</v>
+        <v>אבי חיימי - שמע אלי</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-25</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409733&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409741&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>יוסף שושן - בוחרת בעצמי</v>
+        <v>אבי חיימי - שמע אלי</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>חן ביטון - רבי נחמן אמר</v>
+        <v>אבי חיימי - את בדמי</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-25</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409732&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409740&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,7 +735,7 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>חן ביטון - רבי נחמן אמר</v>
+        <v>אבי חיימי - את בדמי</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יאיר שלום - מחרוזת מורל 2026</v>
+        <v>ישראל גברא - המלאך שלצידי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-25</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409747&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409753&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-25</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יאיר שלום - מחרוזת מורל 2026</v>
+        <v>ישראל גברא - המלאך שלצידי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>זיו אלקיים - לא הכרתי את עצמי</v>
+        <v>רוי סופר - את לא שווה אותי</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-25</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409746&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409752&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-25</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>זיו אלקיים - לא הכרתי את עצמי</v>
+        <v>רוי סופר - את לא שווה אותי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>הראל סבג - ענן של רגשות</v>
+        <v>שילה אליה - עבדו</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-25</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409745&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409751&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-25</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>הראל סבג - ענן של רגשות</v>
+        <v>שילה אליה - עבדו</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אריאל אזולאי - מראה שעל הקיר</v>
+        <v>שי בסיל - הלב שלי שותק</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-25</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409744&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409750&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-25</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אריאל אזולאי - מראה שעל הקיר</v>
+        <v>שי בסיל - הלב שלי שותק</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אבירם שוקרון - מיליון דרכים</v>
+        <v>עמיחי אלמו &amp; נביו לגסה - יופי מושלם</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-25</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409743&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409749&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-25</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אבירם שוקרון - מיליון דרכים</v>
+        <v>עמיחי אלמו &amp; נביו לגסה - יופי מושלם</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אליסף עמר - יאללה</v>
+        <v>ניתאי טויטו - שיר על מזל</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-25</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409742&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409748&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-25</v>
@@ -659,88 +659,12 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אליסף עמר - יאללה</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אבי חיימי - שמע אלי</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409741&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אבי חיימי - שמע אלי</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אבי חיימי - את בדמי</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409740&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אבי חיימי - את בדמי</v>
+        <v>ניתאי טויטו - שיר על מזל</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ישראל גברא - המלאך שלצידי</v>
+        <v>מתנאל אסייג - דמי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-27</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409753&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409805&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ישראל גברא - המלאך שלצידי</v>
+        <v>מתנאל אסייג - דמי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רוי סופר - את לא שווה אותי</v>
+        <v>מוני נחמני - מחרוזת דיכאון 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-27</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409752&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409804&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רוי סופר - את לא שווה אותי</v>
+        <v>מוני נחמני - מחרוזת דיכאון 2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שילה אליה - עבדו</v>
+        <v>מאור נוף - מחרוזת תמיד אוהב אותי 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-27</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409751&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409803&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שילה אליה - עבדו</v>
+        <v>מאור נוף - מחרוזת תמיד אוהב אותי 2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שי בסיל - הלב שלי שותק</v>
+        <v>ישראל כהן - רואה בי את האור</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-27</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409750&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409802&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שי בסיל - הלב שלי שותק</v>
+        <v>ישראל כהן - רואה בי את האור</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>עמיחי אלמו &amp; נביו לגסה - יופי מושלם</v>
+        <v>ליאור רדעי - בחורה מטורפת</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-27</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409749&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409801&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>עמיחי אלמו &amp; נביו לגסה - יופי מושלם</v>
+        <v>ליאור רדעי - בחורה מטורפת</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ניתאי טויטו - שיר על מזל</v>
+        <v>לירן אלמוג - זה אני</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-27</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409748&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409800&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,12 +659,430 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>ניתאי טויטו - שיר על מזל</v>
+        <v>לירן אלמוג - זה אני</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ינון בר ששת - מי את באמת</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409794&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>ינון בר ששת - מי את באמת</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>ינון אברהמי - רבי עקיבא</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409793&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>ינון אברהמי - רבי עקיבא</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>חנוך שובל - מחרוזת המדינות 2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409792&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>חנוך שובל - מחרוזת המדינות 2026</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>הנסיך מהמזרח - מחרוזת דיכאון חלק ד 2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409791&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>הנסיך מהמזרח - מחרוזת דיכאון חלק ד 2026</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>היוצרים - לא פוגעים בלב של גבר</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409790&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>היוצרים - לא פוגעים בלב של גבר</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>הנסיך מהמזרח - מחרוזת דיכאון חלק ג 2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409789&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>הנסיך מהמזרח - מחרוזת דיכאון חלק ג 2026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>גיא יהוד - חיבוק אחרון</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409788&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>גיא יהוד - חיבוק אחרון</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>בתאל סבח - זרוק על הבר</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409787&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>בתאל סבח - זרוק על הבר</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>אמיר עוזיאל - איך ממשיכים</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409786&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>אמיר עוזיאל - איך ממשיכים</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>אמיר דדון - רחובות ריקים</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409785&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>אמיר דדון - רחובות ריקים</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>אבי חיימי - נתתי לה</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409784&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>אבי חיימי - נתתי לה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L18"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מתנאל אסייג - דמי</v>
+        <v>קלימה - אני חוזר אליך</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409805&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409813&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מתנאל אסייג - דמי</v>
+        <v>קלימה - אני חוזר אליך</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מוני נחמני - מחרוזת דיכאון 2026</v>
+        <v>ערן סופר - מחרוזת פזמונים 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409804&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409812&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>מוני נחמני - מחרוזת דיכאון 2026</v>
+        <v>ערן סופר - מחרוזת פזמונים 2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מאור נוף - מחרוזת תמיד אוהב אותי 2026</v>
+        <v>פארידה - מתוך החושך</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409803&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409811&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>מאור נוף - מחרוזת תמיד אוהב אותי 2026</v>
+        <v>פארידה - מתוך החושך</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ישראל כהן - רואה בי את האור</v>
+        <v>עידן כהן - הסיבה לחיות</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409802&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409810&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ישראל כהן - רואה בי את האור</v>
+        <v>עידן כהן - הסיבה לחיות</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ליאור רדעי - בחורה מטורפת</v>
+        <v>עידן דבי - מטוסים עפים</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409801&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409809&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ליאור רדעי - בחורה מטורפת</v>
+        <v>עידן דבי - מטוסים עפים</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>לירן אלמוג - זה אני</v>
+        <v>עידן דבי - ביטים עצובים</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409800&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409808&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>לירן אלמוג - זה אני</v>
+        <v>עידן דבי - ביטים עצובים</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ינון בר ששת - מי את באמת</v>
+        <v>נועה אבוהב - מקלט לאוהבים</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409794&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409807&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,392 +697,12 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>ינון בר ששת - מי את באמת</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>ינון אברהמי - רבי עקיבא</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-27</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409793&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-27</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>ינון אברהמי - רבי עקיבא</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>חנוך שובל - מחרוזת המדינות 2026</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-02-27</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409792&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-27</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>חנוך שובל - מחרוזת המדינות 2026</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>הנסיך מהמזרח - מחרוזת דיכאון חלק ד 2026</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-02-27</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409791&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-02-27</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>הנסיך מהמזרח - מחרוזת דיכאון חלק ד 2026</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>היוצרים - לא פוגעים בלב של גבר</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-02-27</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409790&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-02-27</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>היוצרים - לא פוגעים בלב של גבר</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>הנסיך מהמזרח - מחרוזת דיכאון חלק ג 2026</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-02-27</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409789&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-02-27</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>הנסיך מהמזרח - מחרוזת דיכאון חלק ג 2026</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>גיא יהוד - חיבוק אחרון</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-02-27</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409788&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-02-27</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>גיא יהוד - חיבוק אחרון</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>בתאל סבח - זרוק על הבר</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-02-27</v>
-      </c>
-      <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409787&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-02-27</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v>בתאל סבח - זרוק על הבר</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>אמיר עוזיאל - איך ממשיכים</v>
-      </c>
-      <c r="B16" t="str">
-        <v>2026-02-27</v>
-      </c>
-      <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409786&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
-      </c>
-      <c r="D16" t="str">
-        <v>2026-02-27</v>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
-        <v>אמיר עוזיאל - איך ממשיכים</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>אמיר דדון - רחובות ריקים</v>
-      </c>
-      <c r="B17" t="str">
-        <v>2026-02-27</v>
-      </c>
-      <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409785&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
-      </c>
-      <c r="D17" t="str">
-        <v>2026-02-27</v>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J17" t="str">
-        <v/>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-      <c r="L17" t="str">
-        <v>אמיר דדון - רחובות ריקים</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>אבי חיימי - נתתי לה</v>
-      </c>
-      <c r="B18" t="str">
-        <v>2026-02-27</v>
-      </c>
-      <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409784&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
-      </c>
-      <c r="D18" t="str">
-        <v>2026-02-27</v>
-      </c>
-      <c r="E18" t="str">
-        <v/>
-      </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J18" t="str">
-        <v/>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str">
-        <v>אבי חיימי - נתתי לה</v>
+        <v>נועה אבוהב - מקלט לאוהבים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קלימה - אני חוזר אליך</v>
+        <v>נשמה וקצב - נפש תאומה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-28</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409813&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409825&amp;sid=55891609511621b1adecc708f3015fa1</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-28</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קלימה - אני חוזר אליך</v>
+        <v>נשמה וקצב - נפש תאומה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ערן סופר - מחרוזת פזמונים 2026</v>
+        <v>נוה גדג׳ &amp; בלאדי מורי - כל יום כמו חדש</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-28</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409812&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409824&amp;sid=55891609511621b1adecc708f3015fa1</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-28</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>ערן סופר - מחרוזת פזמונים 2026</v>
+        <v>נוה גדג׳ &amp; בלאדי מורי - כל יום כמו חדש</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>פארידה - מתוך החושך</v>
+        <v>לירון טובול - מרשמלו</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-28</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409811&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409823&amp;sid=55891609511621b1adecc708f3015fa1</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-28</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>פארידה - מתוך החושך</v>
+        <v>לירון טובול - מרשמלו</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עידן כהן - הסיבה לחיות</v>
+        <v>ליאל בריל - קמילו - גרסה אקוסטית</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-28</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409810&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409822&amp;sid=55891609511621b1adecc708f3015fa1</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-28</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>עידן כהן - הסיבה לחיות</v>
+        <v>ליאל בריל - קמילו - גרסה אקוסטית</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>עידן דבי - מטוסים עפים</v>
+        <v>להקת דרך - שואל לאן</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-28</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409809&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409821&amp;sid=55891609511621b1adecc708f3015fa1</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-28</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>עידן דבי - מטוסים עפים</v>
+        <v>להקת דרך - שואל לאן</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>עידן דבי - ביטים עצובים</v>
+        <v>הרב יהושע מרגלית - מחרוזת פורים 2026</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-28</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409808&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409820&amp;sid=55891609511621b1adecc708f3015fa1</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-28</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>עידן דבי - ביטים עצובים</v>
+        <v>הרב יהושע מרגלית - מחרוזת פורים 2026</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>נועה אבוהב - מקלט לאוהבים</v>
+        <v>החללית &amp; אבי אבורומי &amp; עידן בקשי - אהבה של כאב</v>
       </c>
       <c r="B8" t="str">
         <v>2026-02-28</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409807&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409819&amp;sid=55891609511621b1adecc708f3015fa1</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-28</v>
@@ -697,12 +697,202 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>נועה אבוהב - מקלט לאוהבים</v>
+        <v>החללית &amp; אבי אבורומי &amp; עידן בקשי - אהבה של כאב</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>ג'וני נאפש &amp; צוף מימון - לפני שנכנסת לתמונה</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409818&amp;sid=55891609511621b1adecc708f3015fa1</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>ג'וני נאפש &amp; צוף מימון - לפני שנכנסת לתמונה</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>בניסים - לילות לבנים</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409817&amp;sid=55891609511621b1adecc708f3015fa1</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>בניסים - לילות לבנים</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אליה נרקיס - שתיים בלילה</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409816&amp;sid=55891609511621b1adecc708f3015fa1</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אליה נרקיס - שתיים בלילה</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אייר זינגר - מזמור לתודה</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409815&amp;sid=55891609511621b1adecc708f3015fa1</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אייר זינגר - מזמור לתודה</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אברהם יצחק - מטאור</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409814&amp;sid=55891609511621b1adecc708f3015fa1</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אברהם יצחק - מטאור</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
   </ignoredErrors>
 </worksheet>
 </file>